--- a/요구사항_정의서/요구사항_정의서_v10.xlsx
+++ b/요구사항_정의서/요구사항_정의서_v10.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="R11445958f73c4961"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v10 변경요약" sheetId="2" r:id="Re93d5b7f920b45f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공통" sheetId="3" r:id="Rb78ceb05b2f843ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="복약관리대상자" sheetId="4" r:id="R590f6bc3fbdf410d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="보호자" sheetId="5" r:id="Radf15153532841a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="지원인력" sheetId="6" r:id="R79c414f429544db6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="백로그" sheetId="7" r:id="R57b5ca15f85945c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="프로젝트의 목적" sheetId="8" r:id="R89febb49efe54d20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="용어집" sheetId="9" r:id="R11de52d8d40d4baf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="핵심 흐름" sheetId="10" r:id="R1957eaba69cb4881"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="R33ad8d6ca4624a8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v10 변경요약" sheetId="2" r:id="R21dd49ee75cb48ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공통" sheetId="3" r:id="R5ed8ef645b434183"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="복약관리대상자" sheetId="4" r:id="R2fe0d58b1bed47d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="보호자" sheetId="5" r:id="R79ef780ee8d3466b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="지원인력" sheetId="6" r:id="R055bf68a57664eec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="백로그" sheetId="7" r:id="R58ba51828cf042d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="프로젝트의 목적" sheetId="8" r:id="R1d644f03384044ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="용어집" sheetId="9" r:id="R24172695c6ed44ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="핵심 흐름" sheetId="10" r:id="Red7723866afc4025"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -142,9 +142,6 @@
     <x:t xml:space="preserve">상세화</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">보호자 시트에 REQ-059~062 역할별 상세 행 추가</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">요구사항정의서_v10</x:t>
   </x:si>
   <x:si>
@@ -1443,12 +1440,16 @@
   </x:si>
   <x:si>
     <x:r>
+      <x:rPr>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
+      </x:rPr>
       <x:t xml:space="preserve">[2026-07-17 </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1456,16 +1457,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve">, REQ-055 </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1473,16 +1474,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve"> </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1490,16 +1491,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve"> </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1507,16 +1508,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve"> </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1524,16 +1525,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve">] </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1541,16 +1542,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve"> </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1558,16 +1559,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve"> </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1575,16 +1576,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve"> </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1592,16 +1593,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve"> </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1609,16 +1610,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve"> </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1626,16 +1627,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve"> </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1643,16 +1644,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve"> </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1660,16 +1661,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve">(</x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1677,16 +1678,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve"> </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1694,16 +1695,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve">, </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1711,16 +1712,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve"> </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1728,16 +1729,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve">, </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1745,16 +1746,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve">, </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1762,16 +1763,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve"> </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1779,16 +1780,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve"> </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1796,16 +1797,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve">)</x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1813,16 +1814,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve"> </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1830,16 +1831,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve"> </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1847,16 +1848,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve">. </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1864,16 +1865,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve"> </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1881,16 +1882,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve"> </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1898,16 +1899,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve"> </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1915,16 +1916,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve"> </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1932,16 +1933,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve"> </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1949,16 +1950,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve"> </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1966,16 +1967,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve"> </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -1983,16 +1984,16 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve"> </x:t>
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Malgun Gothic"/>
         <x:family val="2"/>
       </x:rPr>
@@ -2000,8 +2001,8 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
+        <x:sz val="1100"/>
+        <x:color rgb="FF000000"/>
         <x:rFont val="Calibri"/>
       </x:rPr>
       <x:t xml:space="preserve">.</x:t>
@@ -2954,7 +2955,7 @@
     </x:row>
     <x:row r="2" ht="80">
       <x:c r="A2" s="1" t="str">
-        <x:v>v9 대비 변경: (1) API명세서_v10·ERD_v10과 맞춰 PR #69 이후 dev 기준 변경사항을 반영 — refresh token 재발급 Method를 POST로 정정, 대기중 초대 삭제/취소(REQ-059), 보호자·지원인력 받은 초대함 수락·거절(REQ-060), 환자 내약 등록·조회·수정·삭제(REQ-061), 처방전 삭제 시 연결 내약·일정 동기화(REQ-062)를 추가했습니다. (2) 보호자·지원인력 시트에도 REQ-059~062를 각 역할의 실제 사용 맥락으로 상세화했습니다. (3) 핵심 흐름 시트를 클라이언트 그룹별 상세 흐름으로 재작성해 환자/보호자/지원인력의 업무 흐름과 구현 상태를 분리했습니다.</x:v>
+        <x:v>v9 대비 변경: (1) API명세서_v10·ERD_v10과 맞춰 PR #69 이후 dev 기준 변경사항을 반영 — refresh token 재발급 Method를 POST로 정정, 대기중 초대 삭제/취소(REQ-059), 보호자·지원인력 받은 초대함 수락·거절(REQ-060), 환자 내약 등록·조회·수정·삭제(REQ-061), 처방전 삭제 시 연결 내약·일정 동기화(REQ-062)를 추가했습니다. (2) 복약관리대상자·보호자·지원인력 시트에도 REQ-059~062를 각 역할의 실제 사용 맥락으로 상세화했습니다. (3) 핵심 흐름 시트를 클라이언트 그룹별 상세 흐름으로 재작성해 환자/보호자/지원인력의 업무 흐름과 구현 상태를 분리했습니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="40" customHeight="1">
@@ -3526,11 +3527,11 @@
       <x:c r="A15" s="10" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B15" s="10" t="s">
+      <x:c r="B15" s="10" t="str">
+        <x:v>복약관리대상자·보호자 시트에 REQ-059~062 역할별 상세 행 추가</x:v>
+      </x:c>
+      <x:c r="C15" s="10" t="s">
         <x:v>41</x:v>
-      </x:c>
-      <x:c r="C15" s="10" t="s">
-        <x:v>42</x:v>
       </x:c>
       <x:c r="D15" s="10" t="s">
         <x:v>12</x:v>
@@ -3541,10 +3542,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B16" s="10" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C16" s="10" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D16" s="10" t="s">
         <x:v>12</x:v>
@@ -3586,67 +3587,67 @@
   <x:sheetData>
     <x:row r="1" ht="17">
       <x:c r="A1" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="3" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="16">
       <x:c r="A4" s="4" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B4" s="4" t="s">
+      <x:c r="C4" s="4" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C4" s="4" t="s">
+      <x:c r="D4" s="4" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D4" s="4" t="s">
+      <x:c r="E4" s="4" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="E4" s="4" t="s">
+      <x:c r="F4" s="4" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="F4" s="4" t="s">
+      <x:c r="G4" s="4" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="G4" s="4" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="I4" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="96">
       <x:c r="A5" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B5" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B5" s="1" t="s">
+      <x:c r="C5" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="C5" s="1" t="s">
+      <x:c r="D5" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="s">
+      <x:c r="E5" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="E5" s="1" t="s">
+      <x:c r="F5" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G5" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="F5" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G5" s="1" t="s">
+      <x:c r="H5" s="1" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="H5" s="1" t="s">
-        <x:v>60</x:v>
       </x:c>
       <x:c r="I5" s="1" t="str">
         <x:v>2026-07-22 결정: 지원인력 교육지원/교육·추적관리 기능은 제품 범위에서 제외되어 REQ-040~044 구현취소</x:v>
@@ -3654,901 +3655,901 @@
     </x:row>
     <x:row r="6" ht="128">
       <x:c r="A6" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="B6" s="1" t="s">
+      <x:c r="C6" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
+      <x:c r="D6" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
+      <x:c r="E6" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="E6" s="1" t="s">
+      <x:c r="F6" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G6" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="F6" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G6" s="1" t="s">
+      <x:c r="H6" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="H6" s="1" t="s">
+      <x:c r="I6" s="1" t="s">
         <x:v>67</x:v>
-      </x:c>
-      <x:c r="I6" s="1" t="s">
-        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="240">
       <x:c r="A7" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B7" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="B7" s="1" t="s">
+      <x:c r="C7" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="C7" s="1" t="s">
+      <x:c r="D7" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="D7" s="1" t="s">
+      <x:c r="E7" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="E7" s="1" t="s">
+      <x:c r="F7" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="F7" s="1" t="s">
+      <x:c r="G7" s="1" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="G7" s="1" t="s">
+      <x:c r="H7" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I7" s="1" t="s">
         <x:v>75</x:v>
-      </x:c>
-      <x:c r="H7" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I7" s="1" t="s">
-        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="96">
       <x:c r="A8" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B8" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B8" s="1" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C8" s="1" t="s">
+      <x:c r="D8" s="1" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="D8" s="1" t="s">
+      <x:c r="E8" s="1" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="E8" s="1" t="s">
+      <x:c r="F8" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G8" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="F8" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="G8" s="1" t="s">
+      <x:c r="H8" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I8" s="1" t="s">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="H8" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I8" s="1" t="s">
-        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="96">
       <x:c r="A9" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B9" s="1" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="B9" s="1" t="s">
+      <x:c r="C9" s="1" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="C9" s="1" t="s">
+      <x:c r="D9" s="1" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D9" s="1" t="s">
+      <x:c r="E9" s="1" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="E9" s="1" t="s">
+      <x:c r="F9" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G9" s="1" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="F9" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G9" s="1" t="s">
+      <x:c r="H9" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I9" s="1" t="s">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="H9" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I9" s="1" t="s">
-        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="64">
       <x:c r="A10" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="B10" s="1" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C10" s="1" t="s">
+      <x:c r="D10" s="1" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="D10" s="1" t="s">
+      <x:c r="E10" s="1" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="E10" s="1" t="s">
+      <x:c r="F10" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G10" s="1" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="F10" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G10" s="1" t="s">
+      <x:c r="H10" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I10" s="1" t="s">
         <x:v>94</x:v>
-      </x:c>
-      <x:c r="H10" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I10" s="1" t="s">
-        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="96">
       <x:c r="A11" s="1" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="B11" s="1" t="s">
+      <x:c r="C11" s="1" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="C11" s="1" t="s">
+      <x:c r="D11" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
+      <x:c r="E11" s="1" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="E11" s="1" t="s">
+      <x:c r="F11" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G11" s="1" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F11" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G11" s="1" t="s">
+      <x:c r="H11" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I11" s="1" t="s">
         <x:v>101</x:v>
-      </x:c>
-      <x:c r="H11" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I11" s="1" t="s">
-        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="48">
       <x:c r="A12" s="1" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B12" s="1" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="B12" s="1" t="s">
+      <x:c r="C12" s="1" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="C12" s="1" t="s">
+      <x:c r="D12" s="1" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="s">
+      <x:c r="E12" s="1" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="E12" s="1" t="s">
+      <x:c r="F12" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G12" s="1" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="F12" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G12" s="1" t="s">
+      <x:c r="H12" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I12" s="1" t="s">
         <x:v>108</x:v>
-      </x:c>
-      <x:c r="H12" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I12" s="1" t="s">
-        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="96">
       <x:c r="A13" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B13" s="1" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="B13" s="1" t="s">
+      <x:c r="C13" s="1" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="C13" s="1" t="s">
+      <x:c r="D13" s="1" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
+      <x:c r="E13" s="1" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="E13" s="1" t="s">
+      <x:c r="F13" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G13" s="1" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="F13" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G13" s="1" t="s">
+      <x:c r="H13" s="1" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="H13" s="1" t="s">
+      <x:c r="I13" s="1" t="s">
         <x:v>116</x:v>
-      </x:c>
-      <x:c r="I13" s="1" t="s">
-        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="128">
       <x:c r="A14" s="1" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="B14" s="1" t="s">
+      <x:c r="C14" s="1" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C14" s="1" t="s">
+      <x:c r="D14" s="1" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
+      <x:c r="E14" s="1" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="E14" s="1" t="s">
+      <x:c r="F14" s="1" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="F14" s="1" t="s">
+      <x:c r="G14" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="G14" s="1" t="s">
+      <x:c r="H14" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I14" s="1" t="s">
         <x:v>124</x:v>
-      </x:c>
-      <x:c r="H14" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I14" s="1" t="s">
-        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="144">
       <x:c r="A15" s="1" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="B15" s="1" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="C15" s="1" t="s">
+      <x:c r="D15" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
+      <x:c r="E15" s="1" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="E15" s="1" t="s">
+      <x:c r="F15" s="1" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G15" s="1" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="G15" s="1" t="s">
+      <x:c r="H15" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I15" s="1" t="s">
         <x:v>130</x:v>
-      </x:c>
-      <x:c r="H15" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I15" s="1" t="s">
-        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="80">
       <x:c r="A16" s="1" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="B16" s="1" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="C16" s="1" t="s">
+      <x:c r="D16" s="1" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
+      <x:c r="E16" s="1" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="E16" s="1" t="s">
+      <x:c r="F16" s="1" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="F16" s="1" t="s">
+      <x:c r="G16" s="1" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="G16" s="1" t="s">
+      <x:c r="H16" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I16" s="1" t="s">
         <x:v>137</x:v>
-      </x:c>
-      <x:c r="H16" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I16" s="1" t="s">
-        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="48">
       <x:c r="A17" s="1" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B17" s="1" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="B17" s="1" t="s">
+      <x:c r="C17" s="1" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="C17" s="1" t="s">
+      <x:c r="D17" s="1" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
+      <x:c r="E17" s="1" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="E17" s="1" t="s">
+      <x:c r="F17" s="1" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="G17" s="1" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="F17" s="1" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="G17" s="1" t="s">
+      <x:c r="H17" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I17" s="1" t="s">
         <x:v>144</x:v>
-      </x:c>
-      <x:c r="H17" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I17" s="1" t="s">
-        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="48">
       <x:c r="A18" s="1" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="B18" s="1" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="B18" s="1" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="C18" s="1" t="s">
+      <x:c r="D18" s="1" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="D18" s="1" t="s">
+      <x:c r="E18" s="1" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="E18" s="1" t="s">
+      <x:c r="F18" s="1" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="G18" s="1" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="F18" s="1" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="G18" s="1" t="s">
+      <x:c r="H18" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I18" s="1" t="s">
         <x:v>150</x:v>
-      </x:c>
-      <x:c r="H18" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I18" s="1" t="s">
-        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="192">
       <x:c r="A19" s="1" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B19" s="1" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="B19" s="1" t="s">
+      <x:c r="C19" s="1" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="C19" s="1" t="s">
+      <x:c r="D19" s="1" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="D19" s="1" t="s">
+      <x:c r="E19" s="1" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="E19" s="1" t="s">
+      <x:c r="F19" s="1" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G19" s="1" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="F19" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="G19" s="1" t="s">
+      <x:c r="H19" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I19" s="1" t="s">
         <x:v>157</x:v>
-      </x:c>
-      <x:c r="H19" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I19" s="1" t="s">
-        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="160">
       <x:c r="A20" s="1" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="B20" s="1" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="B20" s="1" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="C20" s="1" t="s">
+      <x:c r="D20" s="1" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="D20" s="1" t="s">
+      <x:c r="E20" s="1" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="E20" s="1" t="s">
+      <x:c r="F20" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G20" s="1" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="F20" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G20" s="1" t="s">
+      <x:c r="H20" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I20" s="1" t="s">
         <x:v>163</x:v>
-      </x:c>
-      <x:c r="H20" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I20" s="1" t="s">
-        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="112">
       <x:c r="A21" s="1" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="B21" s="1" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="B21" s="1" t="s">
+      <x:c r="C21" s="1" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="C21" s="1" t="s">
+      <x:c r="D21" s="1" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="D21" s="1" t="s">
+      <x:c r="E21" s="1" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="E21" s="1" t="s">
+      <x:c r="F21" s="1" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G21" s="1" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="F21" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="G21" s="1" t="s">
+      <x:c r="H21" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I21" s="1" t="s">
         <x:v>170</x:v>
-      </x:c>
-      <x:c r="H21" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I21" s="1" t="s">
-        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="32">
       <x:c r="A22" s="1" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="B22" s="1" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="B22" s="1" t="s">
+      <x:c r="C22" s="1" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="C22" s="1" t="s">
+      <x:c r="D22" s="1" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="D22" s="1" t="s">
+      <x:c r="E22" s="1" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="E22" s="1" t="s">
+      <x:c r="F22" s="1" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G22" s="1" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="F22" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="G22" s="1" t="s">
+      <x:c r="H22" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="I22" s="1" t="s">
         <x:v>177</x:v>
-      </x:c>
-      <x:c r="H22" s="1" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="I22" s="1" t="s">
-        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="256">
       <x:c r="A23" s="1" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="B23" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="B23" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C23" s="1" t="s">
+      <x:c r="D23" s="1" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="D23" s="1" t="s">
+      <x:c r="E23" s="1" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="E23" s="1" t="s">
+      <x:c r="F23" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G23" s="1" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="F23" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G23" s="1" t="s">
+      <x:c r="H23" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I23" s="1" t="s">
         <x:v>183</x:v>
-      </x:c>
-      <x:c r="H23" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I23" s="1" t="s">
-        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="128">
       <x:c r="A24" s="1" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="B24" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="B24" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C24" s="1" t="s">
+      <x:c r="D24" s="1" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="D24" s="1" t="s">
+      <x:c r="E24" s="1" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="E24" s="1" t="s">
+      <x:c r="F24" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G24" s="1" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="F24" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G24" s="1" t="s">
+      <x:c r="H24" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I24" s="1" t="s">
         <x:v>189</x:v>
-      </x:c>
-      <x:c r="H24" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I24" s="1" t="s">
-        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="144">
       <x:c r="A25" s="1" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="B25" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="B25" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C25" s="1" t="s">
+      <x:c r="D25" s="1" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="D25" s="1" t="s">
+      <x:c r="E25" s="1" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="E25" s="1" t="s">
+      <x:c r="F25" s="1" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G25" s="1" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="F25" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="G25" s="1" t="s">
+      <x:c r="H25" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I25" s="1" t="s">
         <x:v>195</x:v>
-      </x:c>
-      <x:c r="H25" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I25" s="1" t="s">
-        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="80">
       <x:c r="A26" s="1" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="B26" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C26" s="1" t="s">
+      <x:c r="D26" s="1" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="D26" s="1" t="s">
+      <x:c r="E26" s="1" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="E26" s="1" t="s">
+      <x:c r="F26" s="1" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="F26" s="1" t="s">
+      <x:c r="G26" s="1" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="G26" s="1" t="s">
+      <x:c r="H26" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I26" s="1" t="s">
         <x:v>202</x:v>
-      </x:c>
-      <x:c r="H26" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I26" s="1" t="s">
-        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="B27" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="B27" t="s">
+      <x:c r="C27" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="C27" t="s">
+      <x:c r="D27" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="D27" t="s">
+      <x:c r="E27" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="E27" t="s">
+      <x:c r="F27" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G27" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="F27" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="G27" t="s">
+      <x:c r="H27" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I27" t="s">
         <x:v>209</x:v>
-      </x:c>
-      <x:c r="H27" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I27" t="s">
-        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="B28" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C28" t="s">
         <x:v>211</x:v>
       </x:c>
-      <x:c r="B28" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C28" t="s">
+      <x:c r="D28" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="D28" t="s">
+      <x:c r="E28" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="E28" t="s">
+      <x:c r="F28" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G28" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="F28" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G28" t="s">
+      <x:c r="H28" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I28" t="s">
         <x:v>215</x:v>
-      </x:c>
-      <x:c r="H28" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I28" t="s">
-        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="B29" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C29" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="B29" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C29" t="s">
+      <x:c r="D29" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="D29" t="s">
+      <x:c r="E29" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="E29" t="s">
+      <x:c r="F29" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G29" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="F29" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G29" t="s">
+      <x:c r="H29" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="I29" t="s">
         <x:v>221</x:v>
-      </x:c>
-      <x:c r="H29" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="I29" t="s">
-        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="B30" t="s">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="B30" t="s">
+      <x:c r="C30" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="C30" t="s">
+      <x:c r="D30" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="D30" t="s">
+      <x:c r="E30" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="E30" t="s">
+      <x:c r="F30" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G30" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="F30" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="G30" t="s">
+      <x:c r="H30" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="H30" t="s">
+      <x:c r="I30" t="s">
         <x:v>229</x:v>
-      </x:c>
-      <x:c r="I30" t="s">
-        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="B31" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="B31" t="s">
+      <x:c r="C31" t="s">
         <x:v>232</x:v>
       </x:c>
-      <x:c r="C31" t="s">
+      <x:c r="D31" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="D31" t="s">
+      <x:c r="E31" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="E31" t="s">
+      <x:c r="F31" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G31" t="s">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="F31" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="G31" t="s">
+      <x:c r="H31" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I31" t="s">
         <x:v>236</x:v>
-      </x:c>
-      <x:c r="H31" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I31" t="s">
-        <x:v>237</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="B32" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="C32" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="B32" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="C32" t="s">
+      <x:c r="D32" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="D32" t="s">
+      <x:c r="E32" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="E32" t="s">
+      <x:c r="F32" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G32" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="F32" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="G32" t="s">
+      <x:c r="H32" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I32" t="s">
         <x:v>242</x:v>
-      </x:c>
-      <x:c r="H32" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I32" t="s">
-        <x:v>243</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="95" customHeight="1">
       <x:c r="A33" s="1" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="B33" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="s">
         <x:v>244</x:v>
       </x:c>
-      <x:c r="B33" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C33" s="1" t="s">
+      <x:c r="D33" s="1" t="s">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="D33" s="1" t="s">
+      <x:c r="E33" s="1" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="E33" s="1" t="s">
+      <x:c r="F33" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G33" s="1" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="F33" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G33" s="1" t="s">
+      <x:c r="H33" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I33" s="1" t="s">
         <x:v>248</x:v>
-      </x:c>
-      <x:c r="H33" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I33" s="1" t="s">
-        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="95" customHeight="1">
       <x:c r="A34" s="1" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="B34" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C34" s="1" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="B34" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C34" s="1" t="s">
+      <x:c r="D34" s="1" t="s">
         <x:v>251</x:v>
       </x:c>
-      <x:c r="D34" s="1" t="s">
+      <x:c r="E34" s="1" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="E34" s="1" t="s">
+      <x:c r="F34" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G34" s="1" t="s">
         <x:v>253</x:v>
       </x:c>
-      <x:c r="F34" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G34" s="1" t="s">
+      <x:c r="H34" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I34" s="1" t="s">
         <x:v>254</x:v>
-      </x:c>
-      <x:c r="H34" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I34" s="1" t="s">
-        <x:v>255</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="95" customHeight="1">
       <x:c r="A35" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
         <x:v>257</x:v>
       </x:c>
-      <x:c r="D35" s="1" t="s">
+      <x:c r="E35" s="1" t="s">
         <x:v>258</x:v>
       </x:c>
-      <x:c r="E35" s="1" t="s">
+      <x:c r="F35" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G35" s="1" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="F35" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G35" s="1" t="s">
+      <x:c r="H35" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I35" s="1" t="s">
         <x:v>260</x:v>
-      </x:c>
-      <x:c r="H35" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I35" s="1" t="s">
-        <x:v>261</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="95" customHeight="1">
       <x:c r="A36" s="1" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="B36" s="1" t="s">
         <x:v>262</x:v>
       </x:c>
-      <x:c r="B36" s="1" t="s">
+      <x:c r="C36" s="1" t="s">
         <x:v>263</x:v>
       </x:c>
-      <x:c r="C36" s="1" t="s">
+      <x:c r="D36" s="1" t="s">
         <x:v>264</x:v>
       </x:c>
-      <x:c r="D36" s="1" t="s">
+      <x:c r="E36" s="1" t="s">
         <x:v>265</x:v>
       </x:c>
-      <x:c r="E36" s="1" t="s">
+      <x:c r="F36" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G36" s="1" t="s">
         <x:v>266</x:v>
       </x:c>
-      <x:c r="F36" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G36" s="1" t="s">
+      <x:c r="H36" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I36" s="1" t="s">
         <x:v>267</x:v>
-      </x:c>
-      <x:c r="H36" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I36" s="1" t="s">
-        <x:v>268</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4573,650 +4574,782 @@
   <x:sheetData>
     <x:row r="1" ht="17">
       <x:c r="A1" s="2" t="s">
-        <x:v>269</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="3" t="s">
-        <x:v>270</x:v>
+        <x:v>269</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="16">
       <x:c r="A4" s="4" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B4" s="4" t="s">
+      <x:c r="C4" s="4" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C4" s="4" t="s">
+      <x:c r="D4" s="4" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D4" s="4" t="s">
+      <x:c r="E4" s="4" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="E4" s="4" t="s">
+      <x:c r="F4" s="4" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="F4" s="4" t="s">
+      <x:c r="G4" s="4" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="G4" s="4" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="I4" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="64" hidden="1">
       <x:c r="A5" s="1" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="B5" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
         <x:v>271</x:v>
       </x:c>
-      <x:c r="B5" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C5" s="1" t="s">
+      <x:c r="D5" s="1" t="s">
         <x:v>272</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="s">
+      <x:c r="E5" s="1" t="s">
         <x:v>273</x:v>
       </x:c>
-      <x:c r="E5" s="1" t="s">
+      <x:c r="F5" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G5" s="1" t="s">
         <x:v>274</x:v>
       </x:c>
-      <x:c r="F5" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G5" s="1" t="s">
+      <x:c r="H5" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I5" s="1" t="s">
         <x:v>275</x:v>
-      </x:c>
-      <x:c r="H5" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I5" s="1" t="s">
-        <x:v>276</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="144" hidden="1">
       <x:c r="A6" s="1" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
         <x:v>277</x:v>
       </x:c>
-      <x:c r="B6" s="1" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C6" s="1" t="s">
+      <x:c r="D6" s="1" t="s">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
+      <x:c r="E6" s="1" t="s">
         <x:v>279</x:v>
       </x:c>
-      <x:c r="E6" s="1" t="s">
+      <x:c r="F6" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G6" s="1" t="s">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="F6" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G6" s="1" t="s">
+      <x:c r="H6" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I6" s="1" t="s">
         <x:v>281</x:v>
-      </x:c>
-      <x:c r="H6" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I6" s="1" t="s">
-        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="64" hidden="1">
       <x:c r="A7" s="1" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="B7" s="1" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="s">
         <x:v>283</x:v>
       </x:c>
-      <x:c r="B7" s="1" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="C7" s="1" t="s">
+      <x:c r="D7" s="1" t="s">
         <x:v>284</x:v>
       </x:c>
-      <x:c r="D7" s="1" t="s">
+      <x:c r="E7" s="1" t="s">
         <x:v>285</x:v>
       </x:c>
-      <x:c r="E7" s="1" t="s">
+      <x:c r="F7" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G7" s="1" t="s">
         <x:v>286</x:v>
       </x:c>
-      <x:c r="F7" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G7" s="1" t="s">
+      <x:c r="H7" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I7" s="1" t="s">
         <x:v>287</x:v>
-      </x:c>
-      <x:c r="H7" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I7" s="1" t="s">
-        <x:v>288</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="64" hidden="1">
       <x:c r="A8" s="1" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="B8" s="1" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
         <x:v>289</x:v>
       </x:c>
-      <x:c r="B8" s="1" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="C8" s="1" t="s">
+      <x:c r="D8" s="1" t="s">
         <x:v>290</x:v>
       </x:c>
-      <x:c r="D8" s="1" t="s">
+      <x:c r="E8" s="1" t="s">
         <x:v>291</x:v>
       </x:c>
-      <x:c r="E8" s="1" t="s">
+      <x:c r="F8" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G8" s="1" t="s">
         <x:v>292</x:v>
       </x:c>
-      <x:c r="F8" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G8" s="1" t="s">
+      <x:c r="H8" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I8" s="1" t="s">
         <x:v>293</x:v>
-      </x:c>
-      <x:c r="H8" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I8" s="1" t="s">
-        <x:v>294</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="32" hidden="1">
       <x:c r="A9" s="1" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="B9" s="1" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="s">
         <x:v>295</x:v>
       </x:c>
-      <x:c r="B9" s="1" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="C9" s="1" t="s">
+      <x:c r="D9" s="1" t="s">
         <x:v>296</x:v>
       </x:c>
-      <x:c r="D9" s="1" t="s">
+      <x:c r="E9" s="1" t="s">
         <x:v>297</x:v>
       </x:c>
-      <x:c r="E9" s="1" t="s">
+      <x:c r="F9" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G9" s="1" t="s">
         <x:v>298</x:v>
       </x:c>
-      <x:c r="F9" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G9" s="1" t="s">
+      <x:c r="H9" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I9" s="1" t="s">
         <x:v>299</x:v>
-      </x:c>
-      <x:c r="H9" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I9" s="1" t="s">
-        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="32" hidden="1">
       <x:c r="A10" s="1" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
         <x:v>301</x:v>
       </x:c>
-      <x:c r="B10" s="1" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C10" s="1" t="s">
+      <x:c r="D10" s="1" t="s">
         <x:v>302</x:v>
       </x:c>
-      <x:c r="D10" s="1" t="s">
+      <x:c r="E10" s="1" t="s">
         <x:v>303</x:v>
       </x:c>
-      <x:c r="E10" s="1" t="s">
+      <x:c r="F10" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G10" s="1" t="s">
         <x:v>304</x:v>
       </x:c>
-      <x:c r="F10" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G10" s="1" t="s">
+      <x:c r="H10" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I10" s="1" t="s">
         <x:v>305</x:v>
-      </x:c>
-      <x:c r="H10" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I10" s="1" t="s">
-        <x:v>306</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="32" hidden="1">
       <x:c r="A11" s="1" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
         <x:v>307</x:v>
       </x:c>
-      <x:c r="B11" s="1" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C11" s="1" t="s">
+      <x:c r="D11" s="1" t="s">
         <x:v>308</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
+      <x:c r="E11" s="1" t="s">
         <x:v>309</x:v>
       </x:c>
-      <x:c r="E11" s="1" t="s">
+      <x:c r="F11" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G11" s="1" t="s">
         <x:v>310</x:v>
       </x:c>
-      <x:c r="F11" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G11" s="1" t="s">
+      <x:c r="H11" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I11" s="1" t="s">
         <x:v>311</x:v>
-      </x:c>
-      <x:c r="H11" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I11" s="1" t="s">
-        <x:v>312</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="32" hidden="1">
       <x:c r="A12" s="1" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="B12" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C12" s="1" t="s">
         <x:v>313</x:v>
       </x:c>
-      <x:c r="B12" s="1" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C12" s="1" t="s">
+      <x:c r="D12" s="1" t="s">
         <x:v>314</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="s">
+      <x:c r="E12" s="1" t="s">
         <x:v>315</x:v>
       </x:c>
-      <x:c r="E12" s="1" t="s">
+      <x:c r="F12" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G12" s="1" t="s">
         <x:v>316</x:v>
       </x:c>
-      <x:c r="F12" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G12" s="1" t="s">
+      <x:c r="H12" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I12" s="1" t="s">
         <x:v>317</x:v>
-      </x:c>
-      <x:c r="H12" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I12" s="1" t="s">
-        <x:v>318</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="32" hidden="1">
       <x:c r="A13" s="1" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="B13" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
         <x:v>319</x:v>
       </x:c>
-      <x:c r="B13" s="1" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C13" s="1" t="s">
+      <x:c r="D13" s="1" t="s">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
+      <x:c r="E13" s="1" t="s">
         <x:v>321</x:v>
       </x:c>
-      <x:c r="E13" s="1" t="s">
+      <x:c r="F13" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G13" s="1" t="s">
         <x:v>322</x:v>
       </x:c>
-      <x:c r="F13" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G13" s="1" t="s">
+      <x:c r="H13" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I13" s="1" t="s">
         <x:v>323</x:v>
-      </x:c>
-      <x:c r="H13" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I13" s="1" t="s">
-        <x:v>324</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="48" hidden="1">
       <x:c r="A14" s="1" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
         <x:v>325</x:v>
       </x:c>
-      <x:c r="B14" s="1" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C14" s="1" t="s">
+      <x:c r="D14" s="1" t="s">
         <x:v>326</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
+      <x:c r="E14" s="1" t="s">
         <x:v>327</x:v>
       </x:c>
-      <x:c r="E14" s="1" t="s">
+      <x:c r="F14" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G14" s="1" t="s">
         <x:v>328</x:v>
       </x:c>
-      <x:c r="F14" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G14" s="1" t="s">
+      <x:c r="H14" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I14" s="1" t="s">
         <x:v>329</x:v>
-      </x:c>
-      <x:c r="H14" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I14" s="1" t="s">
-        <x:v>330</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="48">
       <x:c r="A15" s="1" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
         <x:v>331</x:v>
       </x:c>
-      <x:c r="B15" s="1" t="s">
+      <x:c r="C15" s="1" t="s">
         <x:v>332</x:v>
       </x:c>
-      <x:c r="C15" s="1" t="s">
+      <x:c r="D15" s="1" t="s">
         <x:v>333</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
+      <x:c r="E15" s="1" t="s">
         <x:v>334</x:v>
       </x:c>
-      <x:c r="E15" s="1" t="s">
+      <x:c r="F15" s="13" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G15" s="1" t="s">
         <x:v>335</x:v>
       </x:c>
-      <x:c r="F15" s="13" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="G15" s="1" t="s">
+      <x:c r="H15" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I15" s="1" t="s">
         <x:v>336</x:v>
-      </x:c>
-      <x:c r="H15" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I15" s="1" t="s">
-        <x:v>337</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="112" hidden="1">
       <x:c r="A16" s="1" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
         <x:v>338</x:v>
       </x:c>
-      <x:c r="B16" s="1" t="s">
-        <x:v>332</x:v>
-      </x:c>
-      <x:c r="C16" s="1" t="s">
+      <x:c r="D16" s="1" t="s">
         <x:v>339</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
+      <x:c r="E16" s="1" t="s">
         <x:v>340</x:v>
       </x:c>
-      <x:c r="E16" s="1" t="s">
+      <x:c r="F16" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G16" s="1" t="s">
         <x:v>341</x:v>
       </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G16" s="1" t="s">
+      <x:c r="H16" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I16" s="1" t="s">
         <x:v>342</x:v>
-      </x:c>
-      <x:c r="H16" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I16" s="1" t="s">
-        <x:v>343</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="32" hidden="1">
       <x:c r="A17" s="1" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B17" s="1" t="s">
         <x:v>344</x:v>
       </x:c>
-      <x:c r="B17" s="1" t="s">
+      <x:c r="C17" s="1" t="s">
         <x:v>345</x:v>
       </x:c>
-      <x:c r="C17" s="1" t="s">
+      <x:c r="D17" s="1" t="s">
         <x:v>346</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
+      <x:c r="E17" s="1" t="s">
         <x:v>347</x:v>
       </x:c>
-      <x:c r="E17" s="1" t="s">
+      <x:c r="F17" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G17" s="1" t="s">
         <x:v>348</x:v>
       </x:c>
-      <x:c r="F17" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G17" s="1" t="s">
+      <x:c r="H17" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I17" s="1" t="s">
         <x:v>349</x:v>
-      </x:c>
-      <x:c r="H17" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I17" s="1" t="s">
-        <x:v>350</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="32" hidden="1">
       <x:c r="A18" s="1" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="B18" s="1" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
         <x:v>351</x:v>
       </x:c>
-      <x:c r="B18" s="1" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="C18" s="1" t="s">
+      <x:c r="D18" s="1" t="s">
         <x:v>352</x:v>
       </x:c>
-      <x:c r="D18" s="1" t="s">
+      <x:c r="E18" s="1" t="s">
         <x:v>353</x:v>
       </x:c>
-      <x:c r="E18" s="1" t="s">
+      <x:c r="F18" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G18" s="1" t="s">
         <x:v>354</x:v>
       </x:c>
-      <x:c r="F18" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G18" s="1" t="s">
+      <x:c r="H18" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I18" s="1" t="s">
         <x:v>355</x:v>
-      </x:c>
-      <x:c r="H18" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I18" s="1" t="s">
-        <x:v>356</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="32">
       <x:c r="A19" s="1" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="B19" s="1" t="s">
         <x:v>357</x:v>
       </x:c>
-      <x:c r="B19" s="1" t="s">
+      <x:c r="C19" s="1" t="s">
         <x:v>358</x:v>
       </x:c>
-      <x:c r="C19" s="1" t="s">
+      <x:c r="D19" s="1" t="s">
         <x:v>359</x:v>
       </x:c>
-      <x:c r="D19" s="1" t="s">
+      <x:c r="E19" s="1" t="s">
         <x:v>360</x:v>
       </x:c>
-      <x:c r="E19" s="1" t="s">
+      <x:c r="F19" s="13" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G19" s="1" t="s">
         <x:v>361</x:v>
       </x:c>
-      <x:c r="F19" s="13" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="G19" s="1" t="s">
+      <x:c r="H19" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I19" s="1" t="s">
         <x:v>362</x:v>
-      </x:c>
-      <x:c r="H19" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I19" s="1" t="s">
-        <x:v>363</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="32">
       <x:c r="A20" s="1" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="B20" s="1" t="s">
         <x:v>364</x:v>
       </x:c>
-      <x:c r="B20" s="1" t="s">
+      <x:c r="C20" s="1" t="s">
         <x:v>365</x:v>
       </x:c>
-      <x:c r="C20" s="1" t="s">
+      <x:c r="D20" s="1" t="s">
         <x:v>366</x:v>
       </x:c>
-      <x:c r="D20" s="1" t="s">
+      <x:c r="E20" s="1" t="s">
         <x:v>367</x:v>
       </x:c>
-      <x:c r="E20" s="1" t="s">
+      <x:c r="F20" s="13" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G20" s="1" t="s">
         <x:v>368</x:v>
       </x:c>
-      <x:c r="F20" s="13" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="G20" s="1" t="s">
+      <x:c r="H20" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I20" s="1" t="s">
         <x:v>369</x:v>
-      </x:c>
-      <x:c r="H20" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I20" s="1" t="s">
-        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="64" hidden="1">
       <x:c r="A21" s="1" t="s">
-        <x:v>371</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
         <x:v>372</x:v>
       </x:c>
-      <x:c r="D21" s="1" t="s">
+      <x:c r="E21" s="1" t="s">
         <x:v>373</x:v>
       </x:c>
-      <x:c r="E21" s="1" t="s">
+      <x:c r="F21" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G21" s="1" t="s">
         <x:v>374</x:v>
       </x:c>
-      <x:c r="F21" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G21" s="1" t="s">
+      <x:c r="H21" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I21" s="1" t="s">
         <x:v>375</x:v>
-      </x:c>
-      <x:c r="H21" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I21" s="1" t="s">
-        <x:v>376</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="160" hidden="1">
       <x:c r="A22" s="1" t="s">
-        <x:v>377</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
         <x:v>378</x:v>
       </x:c>
-      <x:c r="D22" s="1" t="s">
+      <x:c r="E22" s="1" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="E22" s="1" t="s">
+      <x:c r="F22" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G22" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="F22" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G22" s="1" t="s">
+      <x:c r="H22" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I22" s="1" t="s">
         <x:v>381</x:v>
-      </x:c>
-      <x:c r="H22" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I22" s="1" t="s">
-        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="128">
       <x:c r="A23" s="1" t="s">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="B23" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
         <x:v>383</x:v>
       </x:c>
-      <x:c r="B23" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C23" s="1" t="s">
+      <x:c r="D23" s="1" t="s">
         <x:v>384</x:v>
       </x:c>
-      <x:c r="D23" s="1" t="s">
+      <x:c r="E23" s="1" t="s">
         <x:v>385</x:v>
       </x:c>
-      <x:c r="E23" s="1" t="s">
+      <x:c r="F23" s="1" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="G23" s="1" t="s">
         <x:v>386</x:v>
       </x:c>
-      <x:c r="F23" s="1" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="G23" s="1" t="s">
+      <x:c r="H23" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I23" s="1" t="s">
         <x:v>387</x:v>
-      </x:c>
-      <x:c r="H23" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I23" s="1" t="s">
-        <x:v>388</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="96" hidden="1">
       <x:c r="A24" s="1" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="B24" s="1" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
         <x:v>389</x:v>
       </x:c>
-      <x:c r="B24" s="1" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C24" s="1" t="s">
+      <x:c r="D24" s="1" t="s">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="D24" s="1" t="s">
+      <x:c r="E24" s="1" t="s">
         <x:v>391</x:v>
       </x:c>
-      <x:c r="E24" s="1" t="s">
+      <x:c r="F24" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G24" s="1" t="s">
         <x:v>392</x:v>
       </x:c>
-      <x:c r="F24" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G24" s="1" t="s">
+      <x:c r="H24" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I24" s="1" t="s">
         <x:v>393</x:v>
-      </x:c>
-      <x:c r="H24" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I24" s="1" t="s">
-        <x:v>394</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="112" hidden="1">
       <x:c r="A25" s="1" t="s">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="B25" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
         <x:v>395</x:v>
       </x:c>
-      <x:c r="B25" s="1" t="s">
-        <x:v>332</x:v>
-      </x:c>
-      <x:c r="C25" s="1" t="s">
+      <x:c r="D25" s="1" t="s">
         <x:v>396</x:v>
       </x:c>
-      <x:c r="D25" s="1" t="s">
+      <x:c r="E25" s="1" t="s">
         <x:v>397</x:v>
       </x:c>
-      <x:c r="E25" s="1" t="s">
+      <x:c r="F25" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G25" s="1" t="s">
         <x:v>398</x:v>
       </x:c>
-      <x:c r="F25" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G25" s="1" t="s">
+      <x:c r="H25" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I25" s="1" t="s">
         <x:v>399</x:v>
       </x:c>
-      <x:c r="H25" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I25" s="1" t="s">
-        <x:v>400</x:v>
+    </x:row>
+    <x:row r="26" ht="66" hidden="0" customHeight="1">
+      <x:c r="A26" s="15" t="str">
+        <x:v>REQ-059</x:v>
+      </x:c>
+      <x:c r="B26" s="15" t="str">
+        <x:v>돌봄관리</x:v>
+      </x:c>
+      <x:c r="C26" s="15" t="str">
+        <x:v>복약관리대상자로서, 내가 잘못 보냈거나 더 이상 필요 없는 보호자·지원인력 초대를 취소하고 싶다. 그래야 오래된 링크로 의도하지 않은 연결이 생기는 일을 막을 수 있다.</x:v>
+      </x:c>
+      <x:c r="D26" s="15" t="str">
+        <x:v>복약관리대상자는 본인이 보호자·지원인력에게 발송한 대기중 초대를 취소할 수 있어야 한다. 삭제는 실제 행 제거가 아니라 status=cancelled로 전환해 이미 전달된 링크 수락을 차단해야 한다.</x:v>
+      </x:c>
+      <x:c r="E26" s="15" t="str">
+        <x:v>• 본인이 보낸 pending 초대만 취소 가능
+• 취소 후 status=cancelled
+• cancelled 링크 수락 불가
+• 다른 환자의 초대 취소 시 403
+• 이미 처리된 초대는 409</x:v>
+      </x:c>
+      <x:c r="F26" s="15" t="str">
+        <x:v>완료</x:v>
+      </x:c>
+      <x:c r="G26" s="15" t="str">
+        <x:v>care_router.py DELETE /invitations/{invitation_id}. relation_type이 보호자류인 초대는 로그인한 patient.id와 invitation.patient_id 일치 여부를 검증한 뒤 cancelled 처리한다.</x:v>
+      </x:c>
+      <x:c r="H26" s="15" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="I26" s="15" t="str">
+        <x:v>v10에서 공통 REQ-059를 복약관리대상자 관점으로 상세화. 환자가 발송한 보호자·지원인력 초대 취소 흐름을 명시</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="66" hidden="0" customHeight="1">
+      <x:c r="A27" s="15" t="str">
+        <x:v>REQ-060</x:v>
+      </x:c>
+      <x:c r="B27" s="15" t="str">
+        <x:v>돌봄관리</x:v>
+      </x:c>
+      <x:c r="C27" s="15" t="str">
+        <x:v>복약관리대상자로서, 내가 보낸 초대를 보호자·지원인력이 앱 안에서 확인하고 수락 또는 거절할 수 있길 원한다. 그래야 문자 링크를 다시 찾지 않아도 연결을 완료할 수 있다.</x:v>
+      </x:c>
+      <x:c r="D27" s="15" t="str">
+        <x:v>보호자·지원인력의 전화번호와 초대의 invited_phone_hash가 일치하는 pending 초대만 받은 초대 목록에 표시해야 한다. 상대방은 목록에서 토큰 없이 수락·거절할 수 있고, 수락 시 caregiver_patients 연결이 생성되어야 한다.</x:v>
+      </x:c>
+      <x:c r="E27" s="15" t="str">
+        <x:v>• 초대받은 계정의 전화번호 해시 일치
+• pending·만료 전 초대만 표시
+• 수락 시 caregiver_patients 연결 생성
+• 거절 시 status=rejected
+• 타인 초대 조작 방지</x:v>
+      </x:c>
+      <x:c r="F27" s="15" t="str">
+        <x:v>완료</x:v>
+      </x:c>
+      <x:c r="G27" s="15" t="str">
+        <x:v>GET /caregivers/{caregiver_id}/pending-invitations, POST /invitations/{invitation_id}/accept-as-caregiver, POST /invitations/{invitation_id}/reject-as-caregiver 구현.</x:v>
+      </x:c>
+      <x:c r="H27" s="15" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I27" s="15" t="str">
+        <x:v>v10에서 공통 REQ-060의 결과를 복약관리대상자 관점으로 반영. 실제 수락·거절 행위자는 보호자·지원인력 계정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="66" hidden="0" customHeight="1">
+      <x:c r="A28" s="15" t="str">
+        <x:v>REQ-061</x:v>
+      </x:c>
+      <x:c r="B28" s="15" t="str">
+        <x:v>복약관리</x:v>
+      </x:c>
+      <x:c r="C28" s="15" t="str">
+        <x:v>복약관리대상자로서, 현재 내가 복용 중인 약을 처방전 OCR과 별도로 직접 등록·조회·수정·삭제하고 싶다. 그래야 OCR에서 빠진 약이나 장기복용약도 실제 복용 상태대로 관리할 수 있다.</x:v>
+      </x:c>
+      <x:c r="D28" s="15" t="str">
+        <x:v>복약관리대상자는 본인의 내약 목록을 조회하고 약품명·용량·복용횟수·복용기간·출처·검증상태를 등록/수정/삭제할 수 있어야 한다. 삭제는 의료 데이터 보존을 위해 soft delete로 처리한다.</x:v>
+      </x:c>
+      <x:c r="E28" s="15" t="str">
+        <x:v>• 본인 환자 ID만 접근 가능
+• medication_name 필수
+• manual 등록은 user_confirmed 기본값
+• 삭제 시 deleted_at 및 is_active=false
+• 다른 환자 데이터 접근 차단</x:v>
+      </x:c>
+      <x:c r="F28" s="15" t="str">
+        <x:v>완료</x:v>
+      </x:c>
+      <x:c r="G28" s="15" t="str">
+        <x:v>patient_medications_router.py /patients/{patient_id}/medications* 구현. require_actor_patient_access가 환자 본인의 patient_id 접근을 허용한다.</x:v>
+      </x:c>
+      <x:c r="H28" s="15" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I28" s="15" t="str">
+        <x:v>v10에서 공통 REQ-061을 복약관리대상자 관점으로 상세화. 환자 본인의 직접 내약 CRUD를 명시</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A29" s="15" t="str">
+        <x:v>REQ-062</x:v>
+      </x:c>
+      <x:c r="B29" s="15" t="str">
+        <x:v>진료기록입력</x:v>
+      </x:c>
+      <x:c r="C29" s="15" t="str">
+        <x:v>복약관리대상자로서, 내가 처방전 등록내역을 삭제하면 그 처방전에서 만들어진 내약과 일정도 함께 정리되길 원한다. 그래야 삭제한 약이 다음 로그인 후에도 남아 혼란을 주지 않는다.</x:v>
+      </x:c>
+      <x:c r="D29" s="15" t="str">
+        <x:v>복약관리대상자가 본인의 처방전 기록을 삭제하면 medical_records는 soft delete하고, 해당 record_id 또는 prescription_id로 연결된 복약 일정과 내약 데이터를 함께 비활성화해야 한다.</x:v>
+      </x:c>
+      <x:c r="E29" s="15" t="str">
+        <x:v>• 본인의 처방전만 삭제 가능
+• 처방전 목록/상세에서 제외
+• record_id 연결 schedule active=false
+• prescription_id 연결 patient_medications soft delete
+• 해당 내약 기반 schedule 비활성화</x:v>
+      </x:c>
+      <x:c r="F29" s="15" t="str">
+        <x:v>완료</x:v>
+      </x:c>
+      <x:c r="G29" s="15" t="str">
+        <x:v>records_router.py DELETE /records/{record_id}. require_actor_patient_access 후 MedicalRecord, MedicationSchedule, PatientMedication을 함께 정리한다.</x:v>
+      </x:c>
+      <x:c r="H29" s="15" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I29" s="15" t="str">
+        <x:v>v10에서 공통 REQ-062를 복약관리대상자 관점으로 상세화. 환자 본인 삭제 후 데이터 정합성을 명시</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5241,563 +5374,563 @@
   <x:sheetData>
     <x:row r="1" ht="17">
       <x:c r="A1" s="2" t="s">
-        <x:v>401</x:v>
+        <x:v>400</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="3" t="s">
-        <x:v>402</x:v>
+        <x:v>401</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="16">
       <x:c r="A4" s="4" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B4" s="4" t="s">
+      <x:c r="C4" s="4" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C4" s="4" t="s">
+      <x:c r="D4" s="4" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D4" s="4" t="s">
+      <x:c r="E4" s="4" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="E4" s="4" t="s">
+      <x:c r="F4" s="4" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="F4" s="4" t="s">
+      <x:c r="G4" s="4" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="G4" s="4" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="I4" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="64" hidden="1">
       <x:c r="A5" s="1" t="s">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="B5" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
         <x:v>403</x:v>
       </x:c>
-      <x:c r="B5" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C5" s="1" t="s">
+      <x:c r="D5" s="1" t="s">
         <x:v>404</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="s">
+      <x:c r="E5" s="1" t="s">
         <x:v>405</x:v>
       </x:c>
-      <x:c r="E5" s="1" t="s">
+      <x:c r="F5" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G5" s="1" t="s">
         <x:v>406</x:v>
       </x:c>
-      <x:c r="F5" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G5" s="1" t="s">
+      <x:c r="H5" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I5" s="1" t="s">
         <x:v>407</x:v>
-      </x:c>
-      <x:c r="H5" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I5" s="1" t="s">
-        <x:v>408</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="176">
       <x:c r="A6" s="1" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
         <x:v>409</x:v>
       </x:c>
-      <x:c r="B6" s="1" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C6" s="1" t="s">
+      <x:c r="D6" s="1" t="s">
         <x:v>410</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
+      <x:c r="E6" s="1" t="s">
         <x:v>411</x:v>
       </x:c>
-      <x:c r="E6" s="1" t="s">
+      <x:c r="F6" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G6" s="1" t="s">
         <x:v>412</x:v>
       </x:c>
-      <x:c r="F6" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="G6" s="1" t="s">
+      <x:c r="H6" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I6" s="1" t="s">
         <x:v>413</x:v>
-      </x:c>
-      <x:c r="H6" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I6" s="1" t="s">
-        <x:v>414</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="64" hidden="1">
       <x:c r="A7" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>415</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="E7" s="1" t="s">
         <x:v>285</x:v>
       </x:c>
-      <x:c r="E7" s="1" t="s">
+      <x:c r="F7" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G7" s="1" t="s">
         <x:v>286</x:v>
       </x:c>
-      <x:c r="F7" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G7" s="1" t="s">
+      <x:c r="H7" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I7" s="1" t="s">
         <x:v>287</x:v>
-      </x:c>
-      <x:c r="H7" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I7" s="1" t="s">
-        <x:v>288</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="64" hidden="1">
       <x:c r="A8" s="1" t="s">
-        <x:v>289</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="E8" s="1" t="s">
         <x:v>291</x:v>
       </x:c>
-      <x:c r="E8" s="1" t="s">
+      <x:c r="F8" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G8" s="1" t="s">
         <x:v>292</x:v>
       </x:c>
-      <x:c r="F8" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G8" s="1" t="s">
+      <x:c r="H8" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I8" s="1" t="s">
         <x:v>293</x:v>
-      </x:c>
-      <x:c r="H8" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I8" s="1" t="s">
-        <x:v>294</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="112" hidden="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>417</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
         <x:v>340</x:v>
       </x:c>
-      <x:c r="E9" s="1" t="s">
+      <x:c r="F9" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G9" s="1" t="s">
         <x:v>341</x:v>
       </x:c>
-      <x:c r="F9" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G9" s="1" t="s">
+      <x:c r="H9" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I9" s="1" t="s">
         <x:v>342</x:v>
-      </x:c>
-      <x:c r="H9" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I9" s="1" t="s">
-        <x:v>343</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="32" hidden="1">
       <x:c r="A10" s="1" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="s">
         <x:v>344</x:v>
       </x:c>
-      <x:c r="B10" s="1" t="s">
-        <x:v>345</x:v>
-      </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="E10" s="1" t="s">
         <x:v>347</x:v>
       </x:c>
-      <x:c r="E10" s="1" t="s">
+      <x:c r="F10" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G10" s="1" t="s">
         <x:v>348</x:v>
       </x:c>
-      <x:c r="F10" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G10" s="1" t="s">
+      <x:c r="H10" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I10" s="1" t="s">
         <x:v>349</x:v>
-      </x:c>
-      <x:c r="H10" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I10" s="1" t="s">
-        <x:v>350</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="32" hidden="1">
       <x:c r="A11" s="1" t="s">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
         <x:v>419</x:v>
       </x:c>
-      <x:c r="B11" s="1" t="s">
-        <x:v>345</x:v>
-      </x:c>
-      <x:c r="C11" s="1" t="s">
+      <x:c r="D11" s="1" t="s">
         <x:v>420</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
+      <x:c r="E11" s="1" t="s">
         <x:v>421</x:v>
       </x:c>
-      <x:c r="E11" s="1" t="s">
+      <x:c r="F11" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G11" s="1" t="s">
         <x:v>422</x:v>
       </x:c>
-      <x:c r="F11" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G11" s="1" t="s">
+      <x:c r="H11" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I11" s="1" t="s">
         <x:v>423</x:v>
-      </x:c>
-      <x:c r="H11" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I11" s="1" t="s">
-        <x:v>424</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="32" hidden="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="s">
         <x:v>353</x:v>
       </x:c>
-      <x:c r="E12" s="1" t="s">
+      <x:c r="F12" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G12" s="1" t="s">
         <x:v>354</x:v>
       </x:c>
-      <x:c r="F12" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G12" s="1" t="s">
+      <x:c r="H12" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I12" s="1" t="s">
         <x:v>355</x:v>
-      </x:c>
-      <x:c r="H12" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I12" s="1" t="s">
-        <x:v>356</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="64" hidden="1">
       <x:c r="A13" s="1" t="s">
-        <x:v>371</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>426</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="s">
         <x:v>373</x:v>
       </x:c>
-      <x:c r="E13" s="1" t="s">
+      <x:c r="F13" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G13" s="1" t="s">
         <x:v>374</x:v>
       </x:c>
-      <x:c r="F13" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G13" s="1" t="s">
+      <x:c r="H13" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I13" s="1" t="s">
         <x:v>375</x:v>
-      </x:c>
-      <x:c r="H13" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I13" s="1" t="s">
-        <x:v>376</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="48" hidden="1">
       <x:c r="A14" s="1" t="s">
-        <x:v>377</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="F14" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G14" s="1" t="s">
         <x:v>427</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>379</x:v>
-      </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>380</x:v>
-      </x:c>
-      <x:c r="F14" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G14" s="1" t="s">
+      <x:c r="H14" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I14" s="1" t="s">
         <x:v>428</x:v>
-      </x:c>
-      <x:c r="H14" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I14" s="1" t="s">
-        <x:v>429</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="48" hidden="1">
       <x:c r="A15" s="1" t="s">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
         <x:v>430</x:v>
       </x:c>
-      <x:c r="B15" s="1" t="s">
+      <x:c r="C15" s="1" t="s">
         <x:v>431</x:v>
       </x:c>
-      <x:c r="C15" s="1" t="s">
+      <x:c r="D15" s="1" t="s">
         <x:v>432</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
+      <x:c r="E15" s="1" t="s">
         <x:v>433</x:v>
       </x:c>
-      <x:c r="E15" s="1" t="s">
+      <x:c r="F15" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G15" s="1" t="s">
         <x:v>434</x:v>
       </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G15" s="1" t="s">
+      <x:c r="H15" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I15" s="1" t="s">
         <x:v>435</x:v>
-      </x:c>
-      <x:c r="H15" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I15" s="1" t="s">
-        <x:v>436</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="96" hidden="1">
       <x:c r="A16" s="1" t="s">
-        <x:v>389</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G16" s="1" t="s">
         <x:v>437</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>391</x:v>
-      </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>392</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G16" s="1" t="s">
+      <x:c r="H16" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I16" s="1" t="s">
         <x:v>438</x:v>
-      </x:c>
-      <x:c r="H16" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I16" s="1" t="s">
-        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="17">
       <x:c r="A17" t="s">
+        <x:v>439</x:v>
+      </x:c>
+      <x:c r="B17" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="C17" t="s">
         <x:v>440</x:v>
       </x:c>
-      <x:c r="B17" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="C17" t="s">
+      <x:c r="D17" s="14" t="s">
         <x:v>441</x:v>
       </x:c>
-      <x:c r="D17" s="14" t="s">
+      <x:c r="E17" t="s">
         <x:v>442</x:v>
       </x:c>
-      <x:c r="E17" t="s">
+      <x:c r="F17" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="G17" t="s">
         <x:v>443</x:v>
       </x:c>
-      <x:c r="F17" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="G17" t="s">
+      <x:c r="H17" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I17" t="s">
         <x:v>444</x:v>
-      </x:c>
-      <x:c r="H17" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I17" t="s">
-        <x:v>445</x:v>
       </x:c>
     </x:row>
     <x:row r="18" hidden="1">
       <x:c r="A18" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="B18" t="s">
         <x:v>446</x:v>
       </x:c>
-      <x:c r="B18" t="s">
+      <x:c r="C18" t="s">
         <x:v>447</x:v>
       </x:c>
-      <x:c r="C18" t="s">
+      <x:c r="D18" t="s">
         <x:v>448</x:v>
       </x:c>
-      <x:c r="D18" t="s">
+      <x:c r="E18" t="s">
         <x:v>449</x:v>
       </x:c>
-      <x:c r="E18" t="s">
+      <x:c r="F18" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G18" t="s">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="F18" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G18" t="s">
+      <x:c r="H18" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I18" t="s">
         <x:v>451</x:v>
-      </x:c>
-      <x:c r="H18" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I18" t="s">
-        <x:v>452</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="110" hidden="1" customHeight="1">
       <x:c r="A19" s="11" t="s">
-        <x:v>244</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B19" s="10" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C19" s="10" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="D19" s="10" t="s">
         <x:v>453</x:v>
       </x:c>
-      <x:c r="D19" s="10" t="s">
+      <x:c r="E19" s="10" t="s">
         <x:v>454</x:v>
       </x:c>
-      <x:c r="E19" s="10" t="s">
+      <x:c r="F19" s="12" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G19" s="10" t="s">
         <x:v>455</x:v>
       </x:c>
-      <x:c r="F19" s="12" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G19" s="10" t="s">
+      <x:c r="H19" s="10" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I19" s="10" t="s">
         <x:v>456</x:v>
-      </x:c>
-      <x:c r="H19" s="10" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I19" s="10" t="s">
-        <x:v>457</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="110" hidden="1" customHeight="1">
       <x:c r="A20" s="11" t="s">
-        <x:v>250</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B20" s="10" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C20" s="10" t="s">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="D20" s="10" t="s">
         <x:v>458</x:v>
       </x:c>
-      <x:c r="D20" s="10" t="s">
+      <x:c r="E20" s="10" t="s">
         <x:v>459</x:v>
       </x:c>
-      <x:c r="E20" s="10" t="s">
+      <x:c r="F20" s="12" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G20" s="10" t="s">
         <x:v>460</x:v>
       </x:c>
-      <x:c r="F20" s="12" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G20" s="10" t="s">
+      <x:c r="H20" s="10" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I20" s="10" t="s">
         <x:v>461</x:v>
-      </x:c>
-      <x:c r="H20" s="10" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I20" s="10" t="s">
-        <x:v>462</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="110" hidden="1" customHeight="1">
       <x:c r="A21" s="11" t="s">
-        <x:v>256</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B21" s="10" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C21" s="10" t="s">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="D21" s="10" t="s">
         <x:v>463</x:v>
       </x:c>
-      <x:c r="D21" s="10" t="s">
+      <x:c r="E21" s="10" t="s">
         <x:v>464</x:v>
       </x:c>
-      <x:c r="E21" s="10" t="s">
+      <x:c r="F21" s="12" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G21" s="10" t="s">
         <x:v>465</x:v>
       </x:c>
-      <x:c r="F21" s="12" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G21" s="10" t="s">
+      <x:c r="H21" s="10" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I21" s="10" t="s">
         <x:v>466</x:v>
-      </x:c>
-      <x:c r="H21" s="10" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I21" s="10" t="s">
-        <x:v>467</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="110" hidden="1" customHeight="1">
       <x:c r="A22" s="11" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="B22" s="10" t="s">
         <x:v>262</x:v>
       </x:c>
-      <x:c r="B22" s="10" t="s">
-        <x:v>263</x:v>
-      </x:c>
       <x:c r="C22" s="10" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="D22" s="10" t="s">
         <x:v>468</x:v>
       </x:c>
-      <x:c r="D22" s="10" t="s">
+      <x:c r="E22" s="10" t="s">
         <x:v>469</x:v>
       </x:c>
-      <x:c r="E22" s="10" t="s">
+      <x:c r="F22" s="12" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G22" s="10" t="s">
         <x:v>470</x:v>
       </x:c>
-      <x:c r="F22" s="12" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G22" s="10" t="s">
+      <x:c r="H22" s="10" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I22" s="10" t="s">
         <x:v>471</x:v>
-      </x:c>
-      <x:c r="H22" s="10" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I22" s="10" t="s">
-        <x:v>472</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5822,348 +5955,348 @@
   <x:sheetData>
     <x:row r="1" ht="17">
       <x:c r="A1" s="2" t="s">
-        <x:v>473</x:v>
+        <x:v>472</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="3" t="s">
-        <x:v>474</x:v>
+        <x:v>473</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="16">
       <x:c r="A4" s="4" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B4" s="4" t="s">
+      <x:c r="C4" s="4" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C4" s="4" t="s">
+      <x:c r="D4" s="4" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D4" s="4" t="s">
+      <x:c r="E4" s="4" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="E4" s="4" t="s">
+      <x:c r="F4" s="4" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="F4" s="4" t="s">
+      <x:c r="G4" s="4" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="G4" s="4" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="I4" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="64" hidden="1">
       <x:c r="A5" s="1" t="s">
-        <x:v>403</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="E5" s="1" t="s">
         <x:v>405</x:v>
       </x:c>
-      <x:c r="E5" s="1" t="s">
+      <x:c r="F5" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G5" s="1" t="s">
         <x:v>406</x:v>
       </x:c>
-      <x:c r="F5" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G5" s="1" t="s">
+      <x:c r="H5" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I5" s="1" t="s">
         <x:v>407</x:v>
-      </x:c>
-      <x:c r="H5" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I5" s="1" t="s">
-        <x:v>408</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="176">
       <x:c r="A6" s="1" t="s">
-        <x:v>409</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
         <x:v>411</x:v>
       </x:c>
-      <x:c r="E6" s="1" t="s">
+      <x:c r="F6" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G6" s="1" t="s">
         <x:v>412</x:v>
       </x:c>
-      <x:c r="F6" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="G6" s="1" t="s">
+      <x:c r="H6" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I6" s="1" t="s">
         <x:v>413</x:v>
-      </x:c>
-      <x:c r="H6" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I6" s="1" t="s">
-        <x:v>414</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="64" hidden="1">
       <x:c r="A7" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="E7" s="1" t="s">
         <x:v>285</x:v>
       </x:c>
-      <x:c r="E7" s="1" t="s">
+      <x:c r="F7" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G7" s="1" t="s">
         <x:v>286</x:v>
       </x:c>
-      <x:c r="F7" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G7" s="1" t="s">
+      <x:c r="H7" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I7" s="1" t="s">
         <x:v>287</x:v>
-      </x:c>
-      <x:c r="H7" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I7" s="1" t="s">
-        <x:v>288</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="112" hidden="1">
       <x:c r="A8" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="E8" s="1" t="s">
         <x:v>340</x:v>
       </x:c>
-      <x:c r="E8" s="1" t="s">
+      <x:c r="F8" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G8" s="1" t="s">
         <x:v>341</x:v>
       </x:c>
-      <x:c r="F8" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G8" s="1" t="s">
+      <x:c r="H8" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I8" s="1" t="s">
         <x:v>342</x:v>
-      </x:c>
-      <x:c r="H8" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I8" s="1" t="s">
-        <x:v>343</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="32" hidden="1">
       <x:c r="A9" s="1" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B9" s="1" t="s">
         <x:v>344</x:v>
       </x:c>
-      <x:c r="B9" s="1" t="s">
-        <x:v>345</x:v>
-      </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
         <x:v>347</x:v>
       </x:c>
-      <x:c r="E9" s="1" t="s">
+      <x:c r="F9" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G9" s="1" t="s">
         <x:v>348</x:v>
       </x:c>
-      <x:c r="F9" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G9" s="1" t="s">
+      <x:c r="H9" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I9" s="1" t="s">
         <x:v>349</x:v>
-      </x:c>
-      <x:c r="H9" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I9" s="1" t="s">
-        <x:v>350</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="32" hidden="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>480</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="E10" s="1" t="s">
         <x:v>421</x:v>
       </x:c>
-      <x:c r="E10" s="1" t="s">
+      <x:c r="F10" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G10" s="1" t="s">
         <x:v>422</x:v>
       </x:c>
-      <x:c r="F10" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G10" s="1" t="s">
+      <x:c r="H10" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I10" s="1" t="s">
         <x:v>423</x:v>
-      </x:c>
-      <x:c r="H10" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I10" s="1" t="s">
-        <x:v>424</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="32" hidden="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>481</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
         <x:v>353</x:v>
       </x:c>
-      <x:c r="E11" s="1" t="s">
+      <x:c r="F11" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G11" s="1" t="s">
         <x:v>354</x:v>
       </x:c>
-      <x:c r="F11" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G11" s="1" t="s">
+      <x:c r="H11" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I11" s="1" t="s">
         <x:v>355</x:v>
-      </x:c>
-      <x:c r="H11" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I11" s="1" t="s">
-        <x:v>356</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="64" hidden="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>371</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>482</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="s">
         <x:v>373</x:v>
       </x:c>
-      <x:c r="E12" s="1" t="s">
+      <x:c r="F12" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G12" s="1" t="s">
         <x:v>374</x:v>
       </x:c>
-      <x:c r="F12" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G12" s="1" t="s">
+      <x:c r="H12" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I12" s="1" t="s">
         <x:v>375</x:v>
-      </x:c>
-      <x:c r="H12" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I12" s="1" t="s">
-        <x:v>376</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="48" hidden="1">
       <x:c r="A13" s="1" t="s">
-        <x:v>377</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>483</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>380</x:v>
-      </x:c>
       <x:c r="F13" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="H13" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I13" s="1" t="s">
         <x:v>428</x:v>
-      </x:c>
-      <x:c r="H13" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I13" s="1" t="s">
-        <x:v>429</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="48" hidden="1">
       <x:c r="A14" s="1" t="s">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="s">
         <x:v>430</x:v>
       </x:c>
-      <x:c r="B14" s="1" t="s">
-        <x:v>431</x:v>
-      </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="s">
         <x:v>433</x:v>
       </x:c>
-      <x:c r="E14" s="1" t="s">
+      <x:c r="F14" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G14" s="1" t="s">
         <x:v>434</x:v>
       </x:c>
-      <x:c r="F14" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G14" s="1" t="s">
+      <x:c r="H14" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I14" s="1" t="s">
         <x:v>435</x:v>
-      </x:c>
-      <x:c r="H14" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I14" s="1" t="s">
-        <x:v>436</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="64">
       <x:c r="A15" s="1" t="s">
+        <x:v>484</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
         <x:v>485</x:v>
       </x:c>
-      <x:c r="B15" s="1" t="s">
+      <x:c r="C15" s="1" t="s">
         <x:v>486</x:v>
       </x:c>
-      <x:c r="C15" s="1" t="s">
+      <x:c r="D15" s="1" t="s">
         <x:v>487</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
+      <x:c r="E15" s="1" t="s">
         <x:v>488</x:v>
-      </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>489</x:v>
       </x:c>
       <x:c r="F15" s="1" t="str">
         <x:v>구현취소</x:v>
@@ -6180,19 +6313,19 @@
     </x:row>
     <x:row r="16" ht="48">
       <x:c r="A16" s="1" t="s">
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
+        <x:v>485</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
         <x:v>490</x:v>
       </x:c>
-      <x:c r="B16" s="1" t="s">
-        <x:v>486</x:v>
-      </x:c>
-      <x:c r="C16" s="1" t="s">
+      <x:c r="D16" s="1" t="s">
         <x:v>491</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
+      <x:c r="E16" s="1" t="s">
         <x:v>492</x:v>
-      </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>493</x:v>
       </x:c>
       <x:c r="F16" s="1" t="str">
         <x:v>구현취소</x:v>
@@ -6209,19 +6342,19 @@
     </x:row>
     <x:row r="17" ht="48">
       <x:c r="A17" s="1" t="s">
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="B17" s="1" t="s">
+        <x:v>485</x:v>
+      </x:c>
+      <x:c r="C17" s="1" t="s">
         <x:v>494</x:v>
       </x:c>
-      <x:c r="B17" s="1" t="s">
-        <x:v>486</x:v>
-      </x:c>
-      <x:c r="C17" s="1" t="s">
+      <x:c r="D17" s="1" t="s">
         <x:v>495</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
+      <x:c r="E17" s="1" t="s">
         <x:v>496</x:v>
-      </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>497</x:v>
       </x:c>
       <x:c r="F17" s="1" t="str">
         <x:v>구현취소</x:v>
@@ -6238,19 +6371,19 @@
     </x:row>
     <x:row r="18" ht="64">
       <x:c r="A18" s="1" t="s">
+        <x:v>497</x:v>
+      </x:c>
+      <x:c r="B18" s="1" t="s">
+        <x:v>485</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
         <x:v>498</x:v>
       </x:c>
-      <x:c r="B18" s="1" t="s">
-        <x:v>486</x:v>
-      </x:c>
-      <x:c r="C18" s="1" t="s">
+      <x:c r="D18" s="1" t="s">
         <x:v>499</x:v>
       </x:c>
-      <x:c r="D18" s="1" t="s">
+      <x:c r="E18" s="1" t="s">
         <x:v>500</x:v>
-      </x:c>
-      <x:c r="E18" s="1" t="s">
-        <x:v>501</x:v>
       </x:c>
       <x:c r="F18" s="1" t="str">
         <x:v>구현취소</x:v>
@@ -6267,19 +6400,19 @@
     </x:row>
     <x:row r="19" ht="80">
       <x:c r="A19" s="1" t="s">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="B19" s="1" t="s">
+        <x:v>485</x:v>
+      </x:c>
+      <x:c r="C19" s="1" t="s">
         <x:v>502</x:v>
       </x:c>
-      <x:c r="B19" s="1" t="s">
-        <x:v>486</x:v>
-      </x:c>
-      <x:c r="C19" s="1" t="s">
+      <x:c r="D19" s="1" t="s">
         <x:v>503</x:v>
       </x:c>
-      <x:c r="D19" s="1" t="s">
+      <x:c r="E19" s="1" t="s">
         <x:v>504</x:v>
-      </x:c>
-      <x:c r="E19" s="1" t="s">
-        <x:v>505</x:v>
       </x:c>
       <x:c r="F19" s="1" t="str">
         <x:v>구현취소</x:v>
@@ -6296,176 +6429,176 @@
     </x:row>
     <x:row r="20" ht="96" hidden="1">
       <x:c r="A20" s="1" t="s">
-        <x:v>389</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>506</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="E20" s="1" t="s">
         <x:v>391</x:v>
       </x:c>
-      <x:c r="E20" s="1" t="s">
-        <x:v>392</x:v>
-      </x:c>
       <x:c r="F20" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="H20" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I20" s="1" t="s">
         <x:v>438</x:v>
-      </x:c>
-      <x:c r="H20" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I20" s="1" t="s">
-        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="128" hidden="1">
       <x:c r="A21" s="1" t="s">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="B21" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C21" s="1" t="s">
         <x:v>507</x:v>
       </x:c>
-      <x:c r="B21" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C21" s="1" t="s">
+      <x:c r="D21" s="1" t="s">
         <x:v>508</x:v>
       </x:c>
-      <x:c r="D21" s="1" t="s">
+      <x:c r="E21" s="1" t="s">
         <x:v>509</x:v>
       </x:c>
-      <x:c r="E21" s="1" t="s">
+      <x:c r="F21" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G21" s="1" t="s">
         <x:v>510</x:v>
       </x:c>
-      <x:c r="F21" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G21" s="1" t="s">
+      <x:c r="H21" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I21" s="1" t="s">
         <x:v>511</x:v>
-      </x:c>
-      <x:c r="H21" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I21" s="1" t="s">
-        <x:v>512</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="110" hidden="1" customHeight="1">
       <x:c r="A22" s="11" t="s">
-        <x:v>244</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B22" s="10" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C22" s="10" t="s">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="D22" s="10" t="s">
         <x:v>513</x:v>
       </x:c>
-      <x:c r="D22" s="10" t="s">
+      <x:c r="E22" s="10" t="s">
         <x:v>514</x:v>
       </x:c>
-      <x:c r="E22" s="10" t="s">
+      <x:c r="F22" s="12" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G22" s="10" t="s">
         <x:v>515</x:v>
       </x:c>
-      <x:c r="F22" s="12" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G22" s="10" t="s">
+      <x:c r="H22" s="10" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I22" s="10" t="s">
         <x:v>516</x:v>
-      </x:c>
-      <x:c r="H22" s="10" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I22" s="10" t="s">
-        <x:v>517</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="110" hidden="1" customHeight="1">
       <x:c r="A23" s="11" t="s">
-        <x:v>250</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B23" s="10" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C23" s="10" t="s">
+        <x:v>517</x:v>
+      </x:c>
+      <x:c r="D23" s="10" t="s">
         <x:v>518</x:v>
       </x:c>
-      <x:c r="D23" s="10" t="s">
+      <x:c r="E23" s="10" t="s">
         <x:v>519</x:v>
       </x:c>
-      <x:c r="E23" s="10" t="s">
+      <x:c r="F23" s="12" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G23" s="10" t="s">
         <x:v>520</x:v>
       </x:c>
-      <x:c r="F23" s="12" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G23" s="10" t="s">
+      <x:c r="H23" s="10" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I23" s="10" t="s">
         <x:v>521</x:v>
-      </x:c>
-      <x:c r="H23" s="10" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I23" s="10" t="s">
-        <x:v>522</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="110" hidden="1" customHeight="1">
       <x:c r="A24" s="11" t="s">
-        <x:v>256</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B24" s="10" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C24" s="10" t="s">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="D24" s="10" t="s">
         <x:v>523</x:v>
       </x:c>
-      <x:c r="D24" s="10" t="s">
+      <x:c r="E24" s="10" t="s">
         <x:v>524</x:v>
       </x:c>
-      <x:c r="E24" s="10" t="s">
+      <x:c r="F24" s="12" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G24" s="10" t="s">
         <x:v>525</x:v>
       </x:c>
-      <x:c r="F24" s="12" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G24" s="10" t="s">
+      <x:c r="H24" s="10" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I24" s="10" t="s">
         <x:v>526</x:v>
-      </x:c>
-      <x:c r="H24" s="10" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I24" s="10" t="s">
-        <x:v>527</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="110" hidden="1" customHeight="1">
       <x:c r="A25" s="11" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="B25" s="10" t="s">
         <x:v>262</x:v>
       </x:c>
-      <x:c r="B25" s="10" t="s">
-        <x:v>263</x:v>
-      </x:c>
       <x:c r="C25" s="10" t="s">
+        <x:v>527</x:v>
+      </x:c>
+      <x:c r="D25" s="10" t="s">
         <x:v>528</x:v>
       </x:c>
-      <x:c r="D25" s="10" t="s">
+      <x:c r="E25" s="10" t="s">
         <x:v>529</x:v>
       </x:c>
-      <x:c r="E25" s="10" t="s">
+      <x:c r="F25" s="12" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G25" s="10" t="s">
         <x:v>530</x:v>
       </x:c>
-      <x:c r="F25" s="12" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G25" s="10" t="s">
+      <x:c r="H25" s="10" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I25" s="10" t="s">
         <x:v>531</x:v>
-      </x:c>
-      <x:c r="H25" s="10" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I25" s="10" t="s">
-        <x:v>532</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6487,22 +6620,22 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="5" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B1" s="5" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C1" s="5" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D1" s="5" t="s">
+        <x:v>532</x:v>
+      </x:c>
+      <x:c r="E1" s="5" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F1" s="5" t="s">
         <x:v>533</x:v>
-      </x:c>
-      <x:c r="E1" s="5" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F1" s="5" t="s">
-        <x:v>534</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6520,63 +6653,63 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="s">
+        <x:v>534</x:v>
+      </x:c>
+      <x:c r="B1" t="s">
         <x:v>535</x:v>
-      </x:c>
-      <x:c r="B1" t="s">
-        <x:v>536</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="B2" t="s">
         <x:v>537</x:v>
-      </x:c>
-      <x:c r="B2" t="s">
-        <x:v>538</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="s">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="B3" t="s">
         <x:v>539</x:v>
-      </x:c>
-      <x:c r="B3" t="s">
-        <x:v>540</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="s">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="B4" t="s">
         <x:v>541</x:v>
-      </x:c>
-      <x:c r="B4" t="s">
-        <x:v>542</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="s">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="B5" t="s">
         <x:v>543</x:v>
-      </x:c>
-      <x:c r="B5" t="s">
-        <x:v>544</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="B6" t="s">
         <x:v>545</x:v>
-      </x:c>
-      <x:c r="B6" t="s">
-        <x:v>546</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="s">
+        <x:v>546</x:v>
+      </x:c>
+      <x:c r="B7" t="s">
         <x:v>547</x:v>
-      </x:c>
-      <x:c r="B7" t="s">
-        <x:v>548</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="s">
-        <x:v>549</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="B8" t="str">
         <x:v>보호자·요양보호사·생활지원사·사회복지사가 승인된 범위에서 복약·생활관리를 모니터링하도록 돕는다.</x:v>
@@ -6584,23 +6717,23 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="s">
+        <x:v>549</x:v>
+      </x:c>
+      <x:c r="B9" t="s">
         <x:v>550</x:v>
-      </x:c>
-      <x:c r="B9" t="s">
-        <x:v>551</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="s">
+        <x:v>551</x:v>
+      </x:c>
+      <x:c r="B10" t="s">
         <x:v>552</x:v>
-      </x:c>
-      <x:c r="B10" t="s">
-        <x:v>553</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="s">
-        <x:v>554</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="B11" t="str">
         <x:v>지원인력 교육지원/교육·추적관리 기능은 2026-07-22 기준 제품 범위에서 제외되어 구현하지 않는다.</x:v>
@@ -6608,18 +6741,18 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="s">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="B12" t="s">
         <x:v>555</x:v>
-      </x:c>
-      <x:c r="B12" t="s">
-        <x:v>556</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="s">
+        <x:v>556</x:v>
+      </x:c>
+      <x:c r="B13" t="s">
         <x:v>557</x:v>
-      </x:c>
-      <x:c r="B13" t="s">
-        <x:v>558</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6637,23 +6770,23 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="s">
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="B1" t="s">
         <x:v>559</x:v>
-      </x:c>
-      <x:c r="B1" t="s">
-        <x:v>560</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="s">
+        <x:v>560</x:v>
+      </x:c>
+      <x:c r="B2" t="s">
         <x:v>561</x:v>
-      </x:c>
-      <x:c r="B2" t="s">
-        <x:v>562</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="s">
-        <x:v>563</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="B3" t="str">
         <x:v>대상자와 돌봄관계로 연결되어 상태 입력·모니터링·알림 수신을 할 수 있는 가족 등.</x:v>
@@ -6661,7 +6794,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="s">
-        <x:v>564</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="B4" t="str">
         <x:v>대상자를 돌보는 지원인력의 하나. 승인 범위에서 상태 입력·모니터링을 수행할 수 있다.</x:v>
@@ -6669,7 +6802,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="s">
-        <x:v>565</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="B5" t="str">
         <x:v>지원인력의 하나. 승인 범위에서 모니터링과 현장 복약관리 보조를 수행할 수 있다.</x:v>
@@ -6677,7 +6810,7 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="s">
-        <x:v>566</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="B6" t="str">
         <x:v>지원인력의 하나. 승인 범위에서 모니터링과 현장 복약관리 보조를 수행할 수 있다.</x:v>
@@ -6685,15 +6818,15 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="s">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="B7" t="s">
         <x:v>567</x:v>
-      </x:c>
-      <x:c r="B7" t="s">
-        <x:v>568</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="s">
-        <x:v>569</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="B8" t="str">
         <x:v>지원인력 교육지원 기능에서 쓰던 업무 역할. 2026-07-22 기준 해당 기능이 구현취소되어 실제 코드·화면·API에는 사용하지 않는다.</x:v>
@@ -6701,47 +6834,47 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="s">
+        <x:v>569</x:v>
+      </x:c>
+      <x:c r="B9" t="s">
         <x:v>570</x:v>
-      </x:c>
-      <x:c r="B9" t="s">
-        <x:v>571</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="s">
+        <x:v>571</x:v>
+      </x:c>
+      <x:c r="B10" t="s">
         <x:v>572</x:v>
-      </x:c>
-      <x:c r="B10" t="s">
-        <x:v>573</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="s">
+        <x:v>573</x:v>
+      </x:c>
+      <x:c r="B11" t="s">
         <x:v>574</x:v>
-      </x:c>
-      <x:c r="B11" t="s">
-        <x:v>575</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="s">
+        <x:v>575</x:v>
+      </x:c>
+      <x:c r="B12" t="s">
         <x:v>576</x:v>
-      </x:c>
-      <x:c r="B12" t="s">
-        <x:v>577</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="s">
-        <x:v>447</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>578</x:v>
+        <x:v>577</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="s">
-        <x:v>579</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="B14" t="str">
         <x:v>지원인력 교육지원 기능의 기존 단계명. 해당 기능 구현취소로 실제 서비스에서는 사용하지 않는다.</x:v>
@@ -6749,7 +6882,7 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="s">
-        <x:v>580</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="B15" t="str">
         <x:v>지원인력 교육지원 기능의 기존 단계명. 해당 기능 구현취소로 실제 서비스에서는 사용하지 않는다.</x:v>
@@ -6757,7 +6890,7 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="s">
-        <x:v>581</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="B16" t="str">
         <x:v>지원인력 교육지원 기능의 기존 단계명. 해당 기능 구현취소로 실제 서비스에서는 사용하지 않는다.</x:v>
@@ -6765,66 +6898,66 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="s">
+        <x:v>581</x:v>
+      </x:c>
+      <x:c r="B17" t="s">
         <x:v>582</x:v>
-      </x:c>
-      <x:c r="B17" t="s">
-        <x:v>583</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="s">
+        <x:v>583</x:v>
+      </x:c>
+      <x:c r="B18" t="s">
         <x:v>584</x:v>
-      </x:c>
-      <x:c r="B18" t="s">
-        <x:v>585</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="s">
+        <x:v>585</x:v>
+      </x:c>
+      <x:c r="B19" t="s">
         <x:v>586</x:v>
-      </x:c>
-      <x:c r="B19" t="s">
-        <x:v>587</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="s">
+        <x:v>587</x:v>
+      </x:c>
+      <x:c r="B20" t="s">
         <x:v>588</x:v>
-      </x:c>
-      <x:c r="B20" t="s">
-        <x:v>589</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="B21" t="s">
         <x:v>590</x:v>
-      </x:c>
-      <x:c r="B21" t="s">
-        <x:v>591</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="s">
+        <x:v>591</x:v>
+      </x:c>
+      <x:c r="B22" t="s">
         <x:v>592</x:v>
-      </x:c>
-      <x:c r="B22" t="s">
-        <x:v>593</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="s">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="B23" t="s">
         <x:v>594</x:v>
-      </x:c>
-      <x:c r="B23" t="s">
-        <x:v>595</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="s">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="B24" t="s">
         <x:v>596</x:v>
-      </x:c>
-      <x:c r="B24" t="s">
-        <x:v>597</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
